--- a/ksoft/docs/fields_details/Customer_Fields_Detail.xlsx
+++ b/ksoft/docs/fields_details/Customer_Fields_Detail.xlsx
@@ -1446,13 +1446,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87E8D7EC-E440-4C09-880C-30C6D30450BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31F75130-0563-4099-9E24-369BA3BCB395}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E14A72B9-422F-4D08-B8BB-947B7F8A0F32}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80D33307-7897-4A16-800D-17FD6B7A48AE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD9AC375-AE1B-426A-B7F3-73D288D7423C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43192208-B423-42A0-873B-E0F80A16D4CB}"/>
 </file>
--- a/ksoft/docs/fields_details/Customer_Fields_Detail.xlsx
+++ b/ksoft/docs/fields_details/Customer_Fields_Detail.xlsx
@@ -1446,13 +1446,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31F75130-0563-4099-9E24-369BA3BCB395}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87E8D7EC-E440-4C09-880C-30C6D30450BF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80D33307-7897-4A16-800D-17FD6B7A48AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E14A72B9-422F-4D08-B8BB-947B7F8A0F32}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43192208-B423-42A0-873B-E0F80A16D4CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD9AC375-AE1B-426A-B7F3-73D288D7423C}"/>
 </file>